--- a/task_templates_starter.xlsx
+++ b/task_templates_starter.xlsx
@@ -482,9 +482,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -499,9 +497,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -544,9 +540,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
@@ -638,9 +632,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
@@ -690,9 +682,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
@@ -739,7 +729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6067,6 +6057,546 @@
       <c r="M87" s="5" t="inlineStr">
         <is>
           <t>Sustainability hospitals submit one quarter's worth of data per year. Quarter is configurable per hospital; default Q1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>sustainability</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Sustainability Q1</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Complete bi-annual 1:1 QI advising (first half) — early</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>qi_advising</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>End of March</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Either this Q1 task OR the Q2 task fulfills the first-half advising requirement. SOAR sustainability requires one advising session in Jan–June and one in Jul–Dec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>TTT</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Implementation Q1</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Complete Q1 Hospital Readiness Assessment</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>readiness_assessment</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>End of March</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>TTT</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Implementation Q4</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Complete Q4 Hospital Readiness Assessment</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>readiness_assessment</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>End of December</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>NEST</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Implementation Q1</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Complete Q1 Hospital Readiness Assessment</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>readiness_assessment</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>End of March</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>NEST</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Implementation Q4</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Complete Q4 Hospital Readiness Assessment</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>readiness_assessment</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>End of December</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Implementation Q1</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Complete Q1 Hospital Readiness Assessment</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>readiness_assessment</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>End of March</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Implementation Q4</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Complete Q4 Hospital Readiness Assessment</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>readiness_assessment</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>End of December</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SPARK</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Implementation Q2</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Complete Q2 Hospital Readiness Assessment</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>readiness_assessment</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>End of June</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>HRA submitted via REDCap. 2026 SPARK schedule is Q2 + Q4 (not the standard Q1 + Q4) — update templates before 2027 cohort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SPARK</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Implementation Q4</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Complete Q4 Hospital Readiness Assessment</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>readiness_assessment</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>End of December</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>HRA submitted via REDCap. 2026 SPARK schedule is Q2 + Q4 — see Notes on Q2 row.</t>
         </is>
       </c>
     </row>

--- a/task_templates_starter.xlsx
+++ b/task_templates_starter.xlsx
@@ -482,7 +482,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -497,7 +496,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -540,7 +538,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
@@ -632,7 +629,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
@@ -682,7 +678,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
@@ -729,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:M128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -877,7 +872,7 @@
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
@@ -901,12 +896,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Attend at least one Q1 monthly initiative meeting</t>
+          <t>Complete Q1 1:1 QI advising session</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>meeting_attendance</t>
+          <t>qi_advising</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -932,13 +927,13 @@
       <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>Satisfied by any monthly meeting attendance in this quarter, or by attending the annual forum if it falls in this quarter.</t>
+          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -962,27 +957,27 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Complete Q1 1:1 QI advising session</t>
+          <t>Submit January TTT data</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>qi_advising</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>January</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>End of March</t>
+          <t>End of month following January</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -993,13 +988,13 @@
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
@@ -1023,7 +1018,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Submit January TTT data</t>
+          <t>Submit February TTT data</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1038,12 +1033,12 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>February</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>End of month following January</t>
+          <t>End of month following February</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -1060,7 +1055,7 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -1084,7 +1079,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Submit February TTT data</t>
+          <t>Submit March TTT data</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1099,12 +1094,12 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>March</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>End of month following February</t>
+          <t>End of month following March</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -1121,7 +1116,7 @@
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -1135,37 +1130,37 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q2</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Submit March TTT data</t>
+          <t>Complete Q2 1:1 QI advising session</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>data_submission</t>
+          <t>qi_advising</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>End of month following March</t>
+          <t>End of June</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -1176,13 +1171,13 @@
       <c r="L7" s="5" t="inlineStr"/>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Monthly data submission.</t>
+          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -1206,27 +1201,27 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Attend at least one Q2 monthly initiative meeting</t>
+          <t>Submit April TTT data</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>meeting_attendance</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>April</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>End of June</t>
+          <t>End of month following April</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -1237,13 +1232,13 @@
       <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Satisfied by any monthly meeting attendance in this quarter, or by attending the annual forum if it falls in this quarter.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -1267,27 +1262,27 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Complete Q2 1:1 QI advising session</t>
+          <t>Submit May TTT data</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>qi_advising</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>May</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>End of June</t>
+          <t>End of month following May</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -1298,13 +1293,13 @@
       <c r="L9" s="5" t="inlineStr"/>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -1328,7 +1323,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Submit April TTT data</t>
+          <t>Submit June TTT data</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1343,12 +1338,12 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>June</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>End of month following April</t>
+          <t>End of month following June</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -1365,7 +1360,7 @@
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -1379,37 +1374,37 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Implementation Q3</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Submit May TTT data</t>
+          <t>Complete Q3 1:1 QI advising session</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>data_submission</t>
+          <t>qi_advising</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>End of month following May</t>
+          <t>End of September</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -1420,13 +1415,13 @@
       <c r="L11" s="5" t="inlineStr"/>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Monthly data submission.</t>
+          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -1440,17 +1435,17 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Implementation Q3</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Submit June TTT data</t>
+          <t>Submit July TTT data</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1465,12 +1460,12 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>End of month following June</t>
+          <t>End of month following July</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1487,7 +1482,7 @@
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -1511,27 +1506,27 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Attend at least one Q3 monthly initiative meeting</t>
+          <t>Submit August TTT data</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>meeting_attendance</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>August</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>End of September</t>
+          <t>End of month following August</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -1542,13 +1537,13 @@
       <c r="L13" s="5" t="inlineStr"/>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>Satisfied by any monthly meeting attendance in this quarter, or by attending the annual forum if it falls in this quarter.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -1572,27 +1567,27 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Complete Q3 1:1 QI advising session</t>
+          <t>Submit September TTT data</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>qi_advising</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>September</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>End of September</t>
+          <t>End of month following September</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -1603,13 +1598,13 @@
       <c r="L14" s="5" t="inlineStr"/>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -1623,37 +1618,37 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Submit July TTT data</t>
+          <t>Complete Q4 1:1 QI advising session</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>data_submission</t>
+          <t>qi_advising</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>End of month following July</t>
+          <t>End of December</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -1664,13 +1659,13 @@
       <c r="L15" s="5" t="inlineStr"/>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>Monthly data submission.</t>
+          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -1684,17 +1679,17 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Submit August TTT data</t>
+          <t>Submit October TTT data</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1709,12 +1704,12 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>October</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>End of month following August</t>
+          <t>End of month following October</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -1731,7 +1726,7 @@
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -1745,17 +1740,17 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Submit September TTT data</t>
+          <t>Submit November TTT data</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1770,12 +1765,12 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>November</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>End of month following September</t>
+          <t>End of month following November</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1792,7 +1787,7 @@
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -1816,27 +1811,27 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Attend at least one Q4 monthly initiative meeting</t>
+          <t>Submit December TTT data</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>meeting_attendance</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>December</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>End of December</t>
+          <t>End of month following December</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -1847,17 +1842,17 @@
       <c r="L18" s="5" t="inlineStr"/>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Satisfied by any monthly meeting attendance in this quarter, or by attending the annual forum if it falls in this quarter.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>TTT</t>
+          <t>SPARK</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1867,37 +1862,37 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Enrollment</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Complete Q4 1:1 QI advising session</t>
+          <t>Submit SPARK annual enrollment form</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>qi_advising</t>
+          <t>enrollment_form</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Annual</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>End of December</t>
+          <t>Before program year begins (typically end of December prior)</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -1908,17 +1903,17 @@
       <c r="L19" s="5" t="inlineStr"/>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
+          <t>Annual requirement: a fresh Enrollment Form is submitted every program year. For TTT this means a Year 1 form for 2026 AND an updated Year 2 form for 2027. Year 1 form becomes available only after the Interest Form is approved by program managers; subsequent years' forms are made available automatically during fall open enrollment. Submission is the only step required to enroll for the year.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>TTT</t>
+          <t>SPARK</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1928,37 +1923,37 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Submit October TTT data</t>
+          <t>Complete Q1 1:1 QI advising session</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>data_submission</t>
+          <t>qi_advising</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>End of month following October</t>
+          <t>End of March</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -1969,17 +1964,17 @@
       <c r="L20" s="5" t="inlineStr"/>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Monthly data submission.</t>
+          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>TTT</t>
+          <t>SPARK</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1989,17 +1984,17 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Submit November TTT data</t>
+          <t>Submit Q1 SPARK data</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -2009,17 +2004,17 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>End of month following November</t>
+          <t>End of month following Q1</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -2030,17 +2025,17 @@
       <c r="L21" s="5" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>Monthly data submission.</t>
+          <t>SPARK requires ≥3 of 4 quarters submitted to meet the legal requirement.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>TTT</t>
+          <t>SPARK</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -2050,37 +2045,37 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q2</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Submit December TTT data</t>
+          <t>Complete Q2 1:1 QI advising session</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>data_submission</t>
+          <t>qi_advising</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>End of month following December</t>
+          <t>End of June</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -2091,13 +2086,13 @@
       <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Monthly data submission.</t>
+          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="5" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -2111,37 +2106,37 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Enrollment</t>
+          <t>Implementation Q2</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>1.</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Submit SPARK annual enrollment form</t>
+          <t>Submit Q2 SPARK data</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>enrollment_form</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Annual</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Before program year begins (typically end of December prior)</t>
+          <t>End of month following Q2</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -2152,13 +2147,13 @@
       <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>Annual requirement: a fresh Enrollment Form is submitted every program year. For TTT this means a Year 1 form for 2026 AND an updated Year 2 form for 2027. Year 1 form becomes available only after the Interest Form is approved by program managers; subsequent years' forms are made available automatically during fall open enrollment. Submission is the only step required to enroll for the year.</t>
+          <t>SPARK requires ≥3 of 4 quarters submitted to meet the legal requirement.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="5" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -2172,22 +2167,22 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q3</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Attend at least one Q1 monthly initiative meeting</t>
+          <t>Complete Q3 1:1 QI advising session</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>meeting_attendance</t>
+          <t>qi_advising</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -2197,12 +2192,12 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>End of March</t>
+          <t>End of September</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -2213,13 +2208,13 @@
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>Satisfied by any monthly meeting attendance in this quarter, or by attending the annual forum if it falls in this quarter.</t>
+          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="5" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -2233,22 +2228,22 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q3</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Complete Q1 1:1 QI advising session</t>
+          <t>Submit Q3 SPARK data</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>qi_advising</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
@@ -2258,12 +2253,12 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>End of March</t>
+          <t>End of month following Q3</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -2274,13 +2269,13 @@
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
+          <t>SPARK requires ≥3 of 4 quarters submitted to meet the legal requirement.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="5" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -2294,22 +2289,22 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Submit Q1 SPARK data</t>
+          <t>Complete Q4 1:1 QI advising session</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>data_submission</t>
+          <t>qi_advising</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -2319,12 +2314,12 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>End of month following Q1</t>
+          <t>End of December</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -2335,13 +2330,13 @@
       <c r="L26" s="5" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>SPARK requires ≥3 of 4 quarters submitted to meet the legal requirement.</t>
+          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="5" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -2355,22 +2350,22 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Attend at least one Q2 monthly initiative meeting</t>
+          <t>Submit Q4 SPARK data</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>meeting_attendance</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
@@ -2380,12 +2375,12 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>End of June</t>
+          <t>End of month following Q4</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -2396,17 +2391,17 @@
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>Satisfied by any monthly meeting attendance in this quarter, or by attending the annual forum if it falls in this quarter.</t>
+          <t>SPARK requires ≥3 of 4 quarters submitted to meet the legal requirement.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="5" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>SPARK</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -2416,37 +2411,37 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Enrollment</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Complete Q2 1:1 QI advising session</t>
+          <t>Submit SOAR annual enrollment form</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>qi_advising</t>
+          <t>enrollment_form</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Annual</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>End of June</t>
+          <t>Before program year begins (typically end of December prior)</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -2457,17 +2452,17 @@
       <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
+          <t>Annual requirement: a fresh Enrollment Form is submitted every program year. For TTT this means a Year 1 form for 2026 AND an updated Year 2 form for 2027. Year 1 form becomes available only after the Interest Form is approved by program managers; subsequent years' forms are made available automatically during fall open enrollment. Submission is the only step required to enroll for the year.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="5" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>SPARK</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -2477,22 +2472,22 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Submit Q2 SPARK data</t>
+          <t>Complete Q1 1:1 QI advising session</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>data_submission</t>
+          <t>qi_advising</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2502,12 +2497,12 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>End of month following Q2</t>
+          <t>End of March</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -2518,17 +2513,17 @@
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>SPARK requires ≥3 of 4 quarters submitted to meet the legal requirement.</t>
+          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="5" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>SPARK</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -2538,37 +2533,37 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Attend at least one Q3 monthly initiative meeting</t>
+          <t>Submit January SOAR data</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>meeting_attendance</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>January</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>End of September</t>
+          <t>End of month following January</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -2579,17 +2574,17 @@
       <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>Satisfied by any monthly meeting attendance in this quarter, or by attending the annual forum if it falls in this quarter.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="5" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>SPARK</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -2599,37 +2594,37 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Complete Q3 1:1 QI advising session</t>
+          <t>Submit February SOAR data</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>qi_advising</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>February</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>End of September</t>
+          <t>End of month following February</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -2640,17 +2635,17 @@
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="5" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>SPARK</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -2660,17 +2655,17 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Submit Q3 SPARK data</t>
+          <t>Submit March SOAR data</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -2680,17 +2675,17 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>March</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>End of month following Q3</t>
+          <t>End of month following March</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -2701,17 +2696,17 @@
       <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>SPARK requires ≥3 of 4 quarters submitted to meet the legal requirement.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="5" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>SPARK</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -2721,22 +2716,22 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q2</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Attend at least one Q4 monthly initiative meeting</t>
+          <t>Complete Q2 1:1 QI advising session</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>meeting_attendance</t>
+          <t>qi_advising</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -2746,12 +2741,12 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>End of December</t>
+          <t>End of June</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -2762,17 +2757,17 @@
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Satisfied by any monthly meeting attendance in this quarter, or by attending the annual forum if it falls in this quarter.</t>
+          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="5" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>SPARK</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -2782,37 +2777,37 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q2</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Complete Q4 1:1 QI advising session</t>
+          <t>Submit April SOAR data</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>qi_advising</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>April</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>End of December</t>
+          <t>End of month following April</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -2823,17 +2818,17 @@
       <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="5" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>SPARK</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -2843,17 +2838,17 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q2</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Submit Q4 SPARK data</t>
+          <t>Submit May SOAR data</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -2863,17 +2858,17 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>May</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>End of month following Q4</t>
+          <t>End of month following May</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2884,13 +2879,13 @@
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>SPARK requires ≥3 of 4 quarters submitted to meet the legal requirement.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="5" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -2904,37 +2899,37 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Enrollment</t>
+          <t>Implementation Q2</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>1.</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Submit SOAR annual enrollment form</t>
+          <t>Submit June SOAR data</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>enrollment_form</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Annual</t>
+          <t>June</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Before program year begins (typically end of December prior)</t>
+          <t>End of month following June</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -2945,13 +2940,13 @@
       <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Annual requirement: a fresh Enrollment Form is submitted every program year. For TTT this means a Year 1 form for 2026 AND an updated Year 2 form for 2027. Year 1 form becomes available only after the Interest Form is approved by program managers; subsequent years' forms are made available automatically during fall open enrollment. Submission is the only step required to enroll for the year.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="5" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -2965,22 +2960,22 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q3</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Attend at least one Q1 monthly initiative meeting</t>
+          <t>Complete Q3 1:1 QI advising session</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>meeting_attendance</t>
+          <t>qi_advising</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -2990,12 +2985,12 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>End of March</t>
+          <t>End of September</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -3006,13 +3001,13 @@
       <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>Satisfied by any monthly meeting attendance in this quarter, or by attending the annual forum if it falls in this quarter.</t>
+          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="5" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
@@ -3026,37 +3021,37 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q3</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Complete Q1 1:1 QI advising session</t>
+          <t>Submit July SOAR data</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>qi_advising</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>July</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>End of March</t>
+          <t>End of month following July</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -3067,13 +3062,13 @@
       <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="5" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -3087,17 +3082,17 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q3</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Submit January SOAR data</t>
+          <t>Submit August SOAR data</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -3112,12 +3107,12 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>August</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>End of month following January</t>
+          <t>End of month following August</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -3134,7 +3129,7 @@
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="5" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
@@ -3148,17 +3143,17 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q3</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Submit February SOAR data</t>
+          <t>Submit September SOAR data</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -3173,12 +3168,12 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>September</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>End of month following February</t>
+          <t>End of month following September</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -3195,7 +3190,7 @@
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="5" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
@@ -3209,37 +3204,37 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Submit March SOAR data</t>
+          <t>Complete Q4 1:1 QI advising session</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>data_submission</t>
+          <t>qi_advising</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>End of month following March</t>
+          <t>End of December</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -3250,13 +3245,13 @@
       <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>Monthly data submission.</t>
+          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="5" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
@@ -3270,37 +3265,37 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Attend at least one Q2 monthly initiative meeting</t>
+          <t>Submit October SOAR data</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>meeting_attendance</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>October</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>End of June</t>
+          <t>End of month following October</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
@@ -3311,13 +3306,13 @@
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>Satisfied by any monthly meeting attendance in this quarter, or by attending the annual forum if it falls in this quarter.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="5" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
@@ -3331,37 +3326,37 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Complete Q2 1:1 QI advising session</t>
+          <t>Submit November SOAR data</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>qi_advising</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>November</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>End of June</t>
+          <t>End of month following November</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
@@ -3372,13 +3367,13 @@
       <c r="L43" s="5" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="5" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
@@ -3392,17 +3387,17 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Submit April SOAR data</t>
+          <t>Submit December SOAR data</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -3417,12 +3412,12 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>December</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>End of month following April</t>
+          <t>End of month following December</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -3439,11 +3434,11 @@
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="5" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>NEST</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -3453,37 +3448,37 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Enrollment</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Submit May SOAR data</t>
+          <t>Submit NEST annual enrollment form</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>data_submission</t>
+          <t>enrollment_form</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Annual</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>End of month following May</t>
+          <t>Before program year begins (typically end of December prior)</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
@@ -3494,17 +3489,17 @@
       <c r="L45" s="5" t="inlineStr"/>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Monthly data submission.</t>
+          <t>Annual requirement: a fresh Enrollment Form is submitted every program year. For TTT this means a Year 1 form for 2026 AND an updated Year 2 form for 2027. Year 1 form becomes available only after the Interest Form is approved by program managers; subsequent years' forms are made available automatically during fall open enrollment. Submission is the only step required to enroll for the year.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="5" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>NEST</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -3514,37 +3509,37 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Submit June SOAR data</t>
+          <t>Complete Q1 1:1 QI advising session</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>data_submission</t>
+          <t>qi_advising</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>End of month following June</t>
+          <t>End of March</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
@@ -3555,17 +3550,17 @@
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Monthly data submission.</t>
+          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="5" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>NEST</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -3575,37 +3570,37 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Attend at least one Q3 monthly initiative meeting</t>
+          <t>Submit January NEST data</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>meeting_attendance</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>January</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>End of September</t>
+          <t>End of month following January</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
@@ -3616,17 +3611,17 @@
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Satisfied by any monthly meeting attendance in this quarter, or by attending the annual forum if it falls in this quarter.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="5" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>NEST</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -3636,37 +3631,37 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Complete Q3 1:1 QI advising session</t>
+          <t>Submit February NEST data</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>qi_advising</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>February</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>End of September</t>
+          <t>End of month following February</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -3677,17 +3672,17 @@
       <c r="L48" s="5" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="5" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>NEST</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -3697,17 +3692,17 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Submit July SOAR data</t>
+          <t>Submit March NEST data</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -3722,12 +3717,12 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>March</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>End of month following July</t>
+          <t>End of month following March</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
@@ -3744,11 +3739,11 @@
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="5" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>NEST</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -3758,37 +3753,37 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Implementation Q2</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Submit August SOAR data</t>
+          <t>Complete Q2 1:1 QI advising session</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>data_submission</t>
+          <t>qi_advising</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>End of month following August</t>
+          <t>End of June</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -3799,17 +3794,17 @@
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>Monthly data submission.</t>
+          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="5" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>NEST</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -3819,17 +3814,17 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Implementation Q2</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Submit September SOAR data</t>
+          <t>Submit April NEST data</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -3844,12 +3839,12 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>April</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>End of month following September</t>
+          <t>End of month following April</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
@@ -3866,11 +3861,11 @@
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="5" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>NEST</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -3880,37 +3875,37 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q2</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Attend at least one Q4 monthly initiative meeting</t>
+          <t>Submit May NEST data</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>meeting_attendance</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>May</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>End of December</t>
+          <t>End of month following May</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -3921,17 +3916,17 @@
       <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>Satisfied by any monthly meeting attendance in this quarter, or by attending the annual forum if it falls in this quarter.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="5" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>NEST</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -3941,37 +3936,37 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q2</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Complete Q4 1:1 QI advising session</t>
+          <t>Submit June NEST data</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>qi_advising</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>June</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>End of December</t>
+          <t>End of month following June</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
@@ -3982,17 +3977,17 @@
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="5" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>NEST</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -4002,37 +3997,37 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q3</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Submit October SOAR data</t>
+          <t>Complete Q3 1:1 QI advising session</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>data_submission</t>
+          <t>qi_advising</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>End of month following October</t>
+          <t>End of September</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
@@ -4043,17 +4038,17 @@
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>Monthly data submission.</t>
+          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="5" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>NEST</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -4063,17 +4058,17 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q3</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Submit November SOAR data</t>
+          <t>Submit July NEST data</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -4088,12 +4083,12 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>July</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>End of month following November</t>
+          <t>End of month following July</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
@@ -4110,11 +4105,11 @@
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="5" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>NEST</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -4124,17 +4119,17 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q3</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Submit December SOAR data</t>
+          <t>Submit August NEST data</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -4149,12 +4144,12 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>August</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>End of month following December</t>
+          <t>End of month following August</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
@@ -4171,7 +4166,7 @@
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="5" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
@@ -4185,37 +4180,37 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Enrollment</t>
+          <t>Implementation Q3</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>1.</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Submit NEST annual enrollment form</t>
+          <t>Submit September NEST data</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>enrollment_form</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Annual</t>
+          <t>September</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Before program year begins (typically end of December prior)</t>
+          <t>End of month following September</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
@@ -4226,13 +4221,13 @@
       <c r="L57" s="5" t="inlineStr"/>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>Annual requirement: a fresh Enrollment Form is submitted every program year. For TTT this means a Year 1 form for 2026 AND an updated Year 2 form for 2027. Year 1 form becomes available only after the Interest Form is approved by program managers; subsequent years' forms are made available automatically during fall open enrollment. Submission is the only step required to enroll for the year.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="5" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
@@ -4246,22 +4241,22 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Attend at least one Q1 monthly initiative meeting</t>
+          <t>Complete Q4 1:1 QI advising session</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>meeting_attendance</t>
+          <t>qi_advising</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
@@ -4271,12 +4266,12 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>End of March</t>
+          <t>End of December</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
@@ -4287,13 +4282,13 @@
       <c r="L58" s="5" t="inlineStr"/>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>Satisfied by any monthly meeting attendance in this quarter, or by attending the annual forum if it falls in this quarter.</t>
+          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="5" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
@@ -4307,37 +4302,37 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Complete Q1 1:1 QI advising session</t>
+          <t>Submit October NEST data</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>qi_advising</t>
+          <t>data_submission</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>October</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>End of March</t>
+          <t>End of month following October</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
@@ -4348,13 +4343,13 @@
       <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
+          <t>Monthly data submission.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="5" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
@@ -4368,17 +4363,17 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Submit January NEST data</t>
+          <t>Submit November NEST data</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -4393,12 +4388,12 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>November</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>End of month following January</t>
+          <t>End of month following November</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
@@ -4415,7 +4410,7 @@
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="5" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
@@ -4429,17 +4424,17 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Submit February NEST data</t>
+          <t>Submit December NEST data</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -4454,12 +4449,12 @@
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>December</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>End of month following February</t>
+          <t>End of month following December</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
@@ -4476,51 +4471,51 @@
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="5" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>NEST</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>sustainability</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Enrollment</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Submit March NEST data</t>
+          <t>Submit SOAR sustainability annual enrollment form</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>data_submission</t>
+          <t>enrollment_form</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>Annual</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>End of month following March</t>
+          <t>Fall open enrollment of prior year</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
@@ -4531,37 +4526,37 @@
       <c r="L62" s="5" t="inlineStr"/>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>Monthly data submission.</t>
+          <t>Annual requirement for sustainability hospitals too. Eligibility is assessed by program managers during fall open enrollment based on prior-year performance and clinical outcomes. Once approved, the hospital submits a sustainability-specific enrollment form each year. Fulfills the Annual Enrollment legal requirement.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="5" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>NEST</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>sustainability</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Sustainability Q1</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Attend at least one Q2 monthly initiative meeting</t>
+          <t>Attend at least one Q1 monthly initiative meeting</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -4576,12 +4571,12 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>End of June</t>
+          <t>End of March</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
@@ -4592,42 +4587,42 @@
       <c r="L63" s="5" t="inlineStr"/>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>Satisfied by any monthly meeting attendance in this quarter, or by attending the annual forum if it falls in this quarter.</t>
+          <t>Can be satisfied by a monthly meeting OR by the cross-initiative annual forum.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="5" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>NEST</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>sustainability</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Sustainability Q2</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Complete Q2 1:1 QI advising session</t>
+          <t>Attend at least one Q2 monthly initiative meeting</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>qi_advising</t>
+          <t>meeting_attendance</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
@@ -4653,57 +4648,57 @@
       <c r="L64" s="5" t="inlineStr"/>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
+          <t>Can be satisfied by a monthly meeting OR by the cross-initiative annual forum.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="5" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>NEST</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>sustainability</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Sustainability Q3</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Submit April NEST data</t>
+          <t>Attend at least one Q3 monthly initiative meeting</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>data_submission</t>
+          <t>meeting_attendance</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>End of month following April</t>
+          <t>End of September</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
@@ -4714,57 +4709,57 @@
       <c r="L65" s="5" t="inlineStr"/>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>Monthly data submission.</t>
+          <t>Can be satisfied by a monthly meeting OR by the cross-initiative annual forum.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="5" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>NEST</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>sustainability</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Sustainability Q4</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Submit May NEST data</t>
+          <t>Attend at least one Q4 monthly initiative meeting</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>data_submission</t>
+          <t>meeting_attendance</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>End of month following May</t>
+          <t>End of December</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
@@ -4775,57 +4770,57 @@
       <c r="L66" s="5" t="inlineStr"/>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>Monthly data submission.</t>
+          <t>Can be satisfied by a monthly meeting OR by the cross-initiative annual forum.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="5" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>NEST</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>sustainability</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Sustainability Q1</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Submit June NEST data</t>
+          <t>Complete Hospital Readiness Assessment (mid-year)</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>data_submission</t>
+          <t>readiness_assessment</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>End of month following June</t>
+          <t>End of March</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
@@ -4836,42 +4831,42 @@
       <c r="L67" s="5" t="inlineStr"/>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>Monthly data submission.</t>
+          <t>Bi-annual HRA #1. Counts toward 2-per-year sustainability requirement.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="5" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>NEST</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>sustainability</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Sustainability Q4</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Attend at least one Q3 monthly initiative meeting</t>
+          <t>Complete Hospital Readiness Assessment (year-end)</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>meeting_attendance</t>
+          <t>readiness_assessment</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
@@ -4881,12 +4876,12 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>End of September</t>
+          <t>End of December</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
@@ -4897,37 +4892,37 @@
       <c r="L68" s="5" t="inlineStr"/>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>Satisfied by any monthly meeting attendance in this quarter, or by attending the annual forum if it falls in this quarter.</t>
+          <t>Bi-annual HRA #2.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="5" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>NEST</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>sustainability</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Sustainability Q2</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Complete Q3 1:1 QI advising session</t>
+          <t>Complete bi-annual 1:1 QI advising (first half)</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -4942,12 +4937,12 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>End of September</t>
+          <t>End of June</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
@@ -4958,57 +4953,57 @@
       <c r="L69" s="5" t="inlineStr"/>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
+          <t>Bi-annual advising #1.</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="5" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>NEST</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>sustainability</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Sustainability Q4</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Submit July NEST data</t>
+          <t>Complete bi-annual 1:1 QI advising (second half)</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>data_submission</t>
+          <t>qi_advising</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>End of month following July</t>
+          <t>End of December</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
@@ -5019,37 +5014,37 @@
       <c r="L70" s="5" t="inlineStr"/>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t>Monthly data submission.</t>
+          <t>Bi-annual advising #2.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="5" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>NEST</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>sustainability</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Sustainability Q1</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Submit August NEST data</t>
+          <t>Submit one quarter of SOAR data</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -5059,17 +5054,17 @@
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>End of month following August</t>
+          <t>End of March</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
@@ -5080,1033 +5075,1017 @@
       <c r="L71" s="5" t="inlineStr"/>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>Monthly data submission.</t>
+          <t>Sustainability hospitals submit one quarter's worth of data per year. Quarter is configurable per hospital; default Q1.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="A72" t="n">
+        <v>87</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>sustainability</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Sustainability Q1</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Complete bi-annual 1:1 QI advising (first half) — early</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>qi_advising</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>End of March</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Either this Q1 task OR the Q2 task fulfills the first-half advising requirement. SOAR sustainability requires one advising session in Jan–June and one in Jul–Dec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" t="n">
+        <v>88</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>TTT</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Implementation Q1</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Complete Q1 Hospital Readiness Assessment</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>readiness_assessment</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>End of March</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" t="n">
+        <v>89</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>TTT</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Implementation Q4</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Complete Q4 Hospital Readiness Assessment</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>readiness_assessment</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>End of December</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" t="n">
+        <v>90</v>
+      </c>
+      <c r="B75" t="inlineStr">
         <is>
           <t>NEST</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Implementation Q1</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Complete Q1 Hospital Readiness Assessment</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>readiness_assessment</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>End of March</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" t="n">
+        <v>91</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NEST</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Implementation Q4</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Complete Q4 Hospital Readiness Assessment</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>readiness_assessment</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>End of December</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" t="n">
+        <v>92</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Implementation Q1</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Complete Q1 Hospital Readiness Assessment</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>readiness_assessment</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>End of March</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" t="n">
+        <v>93</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Implementation Q4</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Complete Q4 Hospital Readiness Assessment</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>readiness_assessment</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>End of December</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" t="n">
+        <v>94</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SPARK</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Implementation Q2</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Complete Q2 Hospital Readiness Assessment</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>readiness_assessment</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>End of June</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>HRA submitted via REDCap. 2026 SPARK schedule is Q2 + Q4 (not the standard Q1 + Q4) — update templates before 2027 cohort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" t="n">
+        <v>95</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SPARK</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Implementation Q4</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Complete Q4 Hospital Readiness Assessment</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>readiness_assessment</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>End of December</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>HRA submitted via REDCap. 2026 SPARK schedule is Q2 + Q4 — see Notes on Q2 row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" t="n">
+        <v>96</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TTT</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Implementation Q1</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Attend the January TTT initiative meeting</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>End of January</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" t="n">
+        <v>97</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>TTT</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Implementation Q1</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Attend the February TTT initiative meeting</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>End of February</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" t="n">
+        <v>98</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>TTT</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Implementation Q1</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Attend the March TTT initiative meeting</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>End of March</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" t="n">
+        <v>99</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TTT</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Implementation Q2</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Attend the April TTT initiative meeting</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>End of April</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" t="n">
+        <v>100</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>TTT</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Implementation Q2</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Attend the May TTT initiative meeting</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>End of May</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" t="n">
+        <v>101</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>TTT</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Implementation Q2</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Attend the June TTT initiative meeting</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>End of June</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" t="n">
+        <v>102</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TTT</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
         <is>
           <t>Implementation Q3</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>Submit September NEST data</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>data_submission</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Attend the July TTT initiative meeting</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="J72" s="5" t="inlineStr">
-        <is>
-          <t>End of month following September</t>
-        </is>
-      </c>
-      <c r="K72" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L72" s="5" t="inlineStr"/>
-      <c r="M72" s="5" t="inlineStr">
-        <is>
-          <t>Monthly data submission.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>NEST</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>Implementation Q4</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>Attend at least one Q4 monthly initiative meeting</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>meeting_attendance</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="I73" s="5" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="J73" s="5" t="inlineStr">
-        <is>
-          <t>End of December</t>
-        </is>
-      </c>
-      <c r="K73" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L73" s="5" t="inlineStr"/>
-      <c r="M73" s="5" t="inlineStr">
-        <is>
-          <t>Satisfied by any monthly meeting attendance in this quarter, or by attending the annual forum if it falls in this quarter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>NEST</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>Implementation Q4</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>Complete Q4 1:1 QI advising session</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>qi_advising</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="J74" s="5" t="inlineStr">
-        <is>
-          <t>End of December</t>
-        </is>
-      </c>
-      <c r="K74" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L74" s="5" t="inlineStr"/>
-      <c r="M74" s="5" t="inlineStr">
-        <is>
-          <t>Quarterly bi-directional check-in with CPCQC QI advisor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>NEST</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>Implementation Q4</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>Submit October NEST data</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>data_submission</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="I75" s="5" t="inlineStr">
-        <is>
-          <t>October</t>
-        </is>
-      </c>
-      <c r="J75" s="5" t="inlineStr">
-        <is>
-          <t>End of month following October</t>
-        </is>
-      </c>
-      <c r="K75" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L75" s="5" t="inlineStr"/>
-      <c r="M75" s="5" t="inlineStr">
-        <is>
-          <t>Monthly data submission.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>NEST</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>Implementation Q4</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>Submit November NEST data</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>data_submission</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>End of month following November</t>
-        </is>
-      </c>
-      <c r="K76" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L76" s="5" t="inlineStr"/>
-      <c r="M76" s="5" t="inlineStr">
-        <is>
-          <t>Monthly data submission.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>NEST</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>Implementation Q4</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>Submit December NEST data</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t>data_submission</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="I77" s="5" t="inlineStr">
-        <is>
-          <t>December</t>
-        </is>
-      </c>
-      <c r="J77" s="5" t="inlineStr">
-        <is>
-          <t>End of month following December</t>
-        </is>
-      </c>
-      <c r="K77" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L77" s="5" t="inlineStr"/>
-      <c r="M77" s="5" t="inlineStr">
-        <is>
-          <t>Monthly data submission.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="5" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>SOAR</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>sustainability</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>Enrollment</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>Submit SOAR sustainability annual enrollment form</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t>enrollment_form</t>
-        </is>
-      </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="I78" s="5" t="inlineStr">
-        <is>
-          <t>Annual</t>
-        </is>
-      </c>
-      <c r="J78" s="5" t="inlineStr">
-        <is>
-          <t>Fall open enrollment of prior year</t>
-        </is>
-      </c>
-      <c r="K78" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L78" s="5" t="inlineStr"/>
-      <c r="M78" s="5" t="inlineStr">
-        <is>
-          <t>Annual requirement for sustainability hospitals too. Eligibility is assessed by program managers during fall open enrollment based on prior-year performance and clinical outcomes. Once approved, the hospital submits a sustainability-specific enrollment form each year. Fulfills the Annual Enrollment legal requirement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="5" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>SOAR</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>sustainability</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>Sustainability Q1</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>Attend at least one Q1 monthly initiative meeting</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>meeting_attendance</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="I79" s="5" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="J79" s="5" t="inlineStr">
-        <is>
-          <t>End of March</t>
-        </is>
-      </c>
-      <c r="K79" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L79" s="5" t="inlineStr"/>
-      <c r="M79" s="5" t="inlineStr">
-        <is>
-          <t>Can be satisfied by a monthly meeting OR by the cross-initiative annual forum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="5" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>SOAR</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>sustainability</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>Sustainability Q2</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>Attend at least one Q2 monthly initiative meeting</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>meeting_attendance</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="I80" s="5" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="J80" s="5" t="inlineStr">
-        <is>
-          <t>End of June</t>
-        </is>
-      </c>
-      <c r="K80" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L80" s="5" t="inlineStr"/>
-      <c r="M80" s="5" t="inlineStr">
-        <is>
-          <t>Can be satisfied by a monthly meeting OR by the cross-initiative annual forum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="30" customHeight="1">
-      <c r="A81" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>SOAR</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>sustainability</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>Sustainability Q3</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>Attend at least one Q3 monthly initiative meeting</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>meeting_attendance</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="J81" s="5" t="inlineStr">
-        <is>
-          <t>End of September</t>
-        </is>
-      </c>
-      <c r="K81" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L81" s="5" t="inlineStr"/>
-      <c r="M81" s="5" t="inlineStr">
-        <is>
-          <t>Can be satisfied by a monthly meeting OR by the cross-initiative annual forum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="30" customHeight="1">
-      <c r="A82" s="5" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>SOAR</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>sustainability</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>Sustainability Q4</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>Attend at least one Q4 monthly initiative meeting</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>meeting_attendance</t>
-        </is>
-      </c>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="J82" s="5" t="inlineStr">
-        <is>
-          <t>End of December</t>
-        </is>
-      </c>
-      <c r="K82" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L82" s="5" t="inlineStr"/>
-      <c r="M82" s="5" t="inlineStr">
-        <is>
-          <t>Can be satisfied by a monthly meeting OR by the cross-initiative annual forum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="30" customHeight="1">
-      <c r="A83" s="5" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>SOAR</t>
-        </is>
-      </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>sustainability</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>Sustainability Q1</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>Complete Hospital Readiness Assessment (mid-year)</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>readiness_assessment</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="I83" s="5" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="J83" s="5" t="inlineStr">
-        <is>
-          <t>End of March</t>
-        </is>
-      </c>
-      <c r="K83" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L83" s="5" t="inlineStr"/>
-      <c r="M83" s="5" t="inlineStr">
-        <is>
-          <t>Bi-annual HRA #1. Counts toward 2-per-year sustainability requirement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="30" customHeight="1">
-      <c r="A84" s="5" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>SOAR</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>sustainability</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>Sustainability Q4</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>Complete Hospital Readiness Assessment (year-end)</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>readiness_assessment</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="J84" s="5" t="inlineStr">
-        <is>
-          <t>End of December</t>
-        </is>
-      </c>
-      <c r="K84" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L84" s="5" t="inlineStr"/>
-      <c r="M84" s="5" t="inlineStr">
-        <is>
-          <t>Bi-annual HRA #2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="5" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>SOAR</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>sustainability</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>Sustainability Q2</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>Complete bi-annual 1:1 QI advising (first half)</t>
-        </is>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>qi_advising</t>
-        </is>
-      </c>
-      <c r="H85" s="5" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="I85" s="5" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="J85" s="5" t="inlineStr">
-        <is>
-          <t>End of June</t>
-        </is>
-      </c>
-      <c r="K85" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L85" s="5" t="inlineStr"/>
-      <c r="M85" s="5" t="inlineStr">
-        <is>
-          <t>Bi-annual advising #1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="30" customHeight="1">
-      <c r="A86" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>SOAR</t>
-        </is>
-      </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>sustainability</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t>Sustainability Q4</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>Complete bi-annual 1:1 QI advising (second half)</t>
-        </is>
-      </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>qi_advising</t>
-        </is>
-      </c>
-      <c r="H86" s="5" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="I86" s="5" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="J86" s="5" t="inlineStr">
-        <is>
-          <t>End of December</t>
-        </is>
-      </c>
-      <c r="K86" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L86" s="5" t="inlineStr"/>
-      <c r="M86" s="5" t="inlineStr">
-        <is>
-          <t>Bi-annual advising #2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="5" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>SOAR</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>sustainability</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>Sustainability Q1</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>Submit one quarter of SOAR data</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>data_submission</t>
-        </is>
-      </c>
-      <c r="H87" s="5" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="I87" s="5" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="J87" s="5" t="inlineStr">
-        <is>
-          <t>End of March</t>
-        </is>
-      </c>
-      <c r="K87" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L87" s="5" t="inlineStr"/>
-      <c r="M87" s="5" t="inlineStr">
-        <is>
-          <t>Sustainability hospitals submit one quarter's worth of data per year. Quarter is configurable per hospital; default Q1.</t>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>End of July</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>TTT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>sustainability</t>
+          <t>active</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Sustainability Q1</t>
+          <t>Implementation Q3</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Complete bi-annual 1:1 QI advising (first half) — early</t>
+          <t>Attend the August TTT initiative meeting</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>qi_advising</t>
+          <t>meeting_attendance</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>August</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>End of March</t>
+          <t>End of August</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6116,13 +6095,13 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Either this Q1 task OR the Q2 task fulfills the first-half advising requirement. SOAR sustainability requires one advising session in Jan–June and one in Jul–Dec.</t>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -6136,37 +6115,37 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q3</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Complete Q1 Hospital Readiness Assessment</t>
+          <t>Attend the September TTT initiative meeting</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>readiness_assessment</t>
+          <t>meeting_attendance</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>September</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>End of March</t>
+          <t>End of September</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6176,13 +6155,13 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -6206,27 +6185,27 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Complete Q4 Hospital Readiness Assessment</t>
+          <t>Attend the October TTT initiative meeting</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>readiness_assessment</t>
+          <t>meeting_attendance</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>October</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>End of December</t>
+          <t>End of October</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6236,17 +6215,17 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NEST</t>
+          <t>TTT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6256,37 +6235,37 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Complete Q1 Hospital Readiness Assessment</t>
+          <t>Attend the November TTT initiative meeting</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>readiness_assessment</t>
+          <t>meeting_attendance</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>November</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>End of March</t>
+          <t>End of November</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6296,17 +6275,17 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NEST</t>
+          <t>TTT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6326,22 +6305,22 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Complete Q4 Hospital Readiness Assessment</t>
+          <t>Attend the December TTT initiative meeting</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>readiness_assessment</t>
+          <t>meeting_attendance</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>December</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6356,17 +6335,17 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>SPARK</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6386,27 +6365,27 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Complete Q1 Hospital Readiness Assessment</t>
+          <t>Attend the January SPARK initiative meeting</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>readiness_assessment</t>
+          <t>meeting_attendance</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>January</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>End of March</t>
+          <t>End of January</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6416,17 +6395,17 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>SPARK</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6436,37 +6415,37 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Complete Q4 Hospital Readiness Assessment</t>
+          <t>Attend the February SPARK initiative meeting</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>readiness_assessment</t>
+          <t>meeting_attendance</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>February</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>End of December</t>
+          <t>End of February</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6476,13 +6455,13 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -6496,37 +6475,37 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Complete Q2 Hospital Readiness Assessment</t>
+          <t>Attend the March SPARK initiative meeting</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>readiness_assessment</t>
+          <t>meeting_attendance</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>March</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>End of June</t>
+          <t>End of March</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6536,13 +6515,13 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>HRA submitted via REDCap. 2026 SPARK schedule is Q2 + Q4 (not the standard Q1 + Q4) — update templates before 2027 cohort.</t>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -6556,47 +6535,1967 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t>Implementation Q2</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Attend the April SPARK initiative meeting</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>End of April</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>112</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SPARK</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Implementation Q2</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Attend the May SPARK initiative meeting</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>End of May</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>113</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SPARK</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Implementation Q2</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Attend the June SPARK initiative meeting</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>End of June</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>114</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SPARK</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Implementation Q3</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Attend the July SPARK initiative meeting</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>End of July</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>115</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SPARK</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Implementation Q3</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Attend the August SPARK initiative meeting</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>End of August</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>116</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SPARK</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Implementation Q3</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Attend the September SPARK initiative meeting</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>End of September</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>117</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SPARK</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
           <t>Implementation Q4</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Complete Q4 Hospital Readiness Assessment</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>readiness_assessment</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Attend the October SPARK initiative meeting</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>End of October</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>118</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SPARK</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Implementation Q4</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Attend the November SPARK initiative meeting</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>November</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>End of November</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>119</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SPARK</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Implementation Q4</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Attend the December SPARK initiative meeting</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
         <is>
           <t>End of December</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>HRA submitted via REDCap. 2026 SPARK schedule is Q2 + Q4 — see Notes on Q2 row.</t>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>120</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Implementation Q1</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Attend the January SOAR initiative meeting</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>End of January</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>121</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Implementation Q1</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Attend the February SOAR initiative meeting</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>End of February</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>122</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Implementation Q1</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Attend the March SOAR initiative meeting</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>End of March</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>123</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Implementation Q2</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Attend the April SOAR initiative meeting</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>End of April</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>124</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Implementation Q2</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Attend the May SOAR initiative meeting</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>End of May</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>125</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Implementation Q2</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Attend the June SOAR initiative meeting</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>End of June</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>126</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Implementation Q3</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Attend the July SOAR initiative meeting</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>End of July</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>127</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Implementation Q3</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Attend the August SOAR initiative meeting</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>End of August</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>128</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Implementation Q3</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Attend the September SOAR initiative meeting</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>End of September</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>129</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Implementation Q4</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Attend the October SOAR initiative meeting</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>End of October</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>130</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Implementation Q4</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Attend the November SOAR initiative meeting</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>November</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>End of November</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>131</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SOAR</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Implementation Q4</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Attend the December SOAR initiative meeting</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>End of December</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>132</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NEST</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Implementation Q1</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Attend the January NEST initiative meeting</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>End of January</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>133</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>NEST</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Implementation Q1</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Attend the February NEST initiative meeting</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>End of February</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>134</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NEST</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Implementation Q1</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Attend the March NEST initiative meeting</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>End of March</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>135</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>NEST</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Implementation Q2</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Attend the April NEST initiative meeting</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>End of April</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>136</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>NEST</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Implementation Q2</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Attend the May NEST initiative meeting</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>End of May</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>137</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>NEST</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Implementation Q2</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Attend the June NEST initiative meeting</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>End of June</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>138</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>NEST</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Implementation Q3</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Attend the July NEST initiative meeting</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>End of July</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>139</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>NEST</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Implementation Q3</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Attend the August NEST initiative meeting</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>End of August</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>140</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>NEST</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Implementation Q3</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Attend the September NEST initiative meeting</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>End of September</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>141</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>NEST</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Implementation Q4</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Attend the October NEST initiative meeting</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>End of October</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>142</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>NEST</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Implementation Q4</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Attend the November NEST initiative meeting</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>November</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>End of November</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>143</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>NEST</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Implementation Q4</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Attend the December NEST initiative meeting</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>meeting_attendance</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>End of December</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
         </is>
       </c>
     </row>

--- a/task_templates_starter.xlsx
+++ b/task_templates_starter.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TaskTemplates" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StageDefinitions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meetings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TaskTemplates" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="StageDefinitions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Requirements" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Meetings" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M128"/>
+  <dimension ref="A1:M127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5081,36 +5081,36 @@
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>TTT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>sustainability</t>
+          <t>active</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sustainability Q1</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Complete bi-annual 1:1 QI advising (first half) — early</t>
+          <t>Complete Q1 Hospital Readiness Assessment</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>qi_advising</t>
+          <t>readiness_assessment</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5135,13 +5135,13 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Either this Q1 task OR the Q2 task fulfills the first-half advising requirement. SOAR sustainability requires one advising session in Jan–June and one in Jul–Dec.</t>
+          <t>HRA submitted via REDCap; we only track that it was completed.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -5155,17 +5155,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Complete Q1 Hospital Readiness Assessment</t>
+          <t>Complete Q4 Hospital Readiness Assessment</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>End of March</t>
+          <t>End of December</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5201,11 +5201,11 @@
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TTT</t>
+          <t>NEST</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5215,17 +5215,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Complete Q4 Hospital Readiness Assessment</t>
+          <t>Complete Q1 Hospital Readiness Assessment</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>End of December</t>
+          <t>End of March</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5261,7 +5261,7 @@
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -5275,17 +5275,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Complete Q1 Hospital Readiness Assessment</t>
+          <t>Complete Q4 Hospital Readiness Assessment</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>End of March</t>
+          <t>End of December</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5321,11 +5321,11 @@
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NEST</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5335,17 +5335,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Complete Q4 Hospital Readiness Assessment</t>
+          <t>Complete Q1 Hospital Readiness Assessment</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>End of December</t>
+          <t>End of March</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5381,7 +5381,7 @@
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -5395,17 +5395,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Complete Q1 Hospital Readiness Assessment</t>
+          <t>Complete Q4 Hospital Readiness Assessment</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5420,12 +5420,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>End of March</t>
+          <t>End of December</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5441,11 +5441,11 @@
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>SPARK</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5455,17 +5455,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q2</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Complete Q4 Hospital Readiness Assessment</t>
+          <t>Complete Q2 Hospital Readiness Assessment</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>End of December</t>
+          <t>End of June</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5495,13 +5495,13 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>HRA submitted via REDCap; we only track that it was completed.</t>
+          <t>HRA submitted via REDCap. 2026 SPARK schedule is Q2 + Q4 (not the standard Q1 + Q4) — update templates before 2027 cohort.</t>
         </is>
       </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -5515,17 +5515,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Complete Q2 Hospital Readiness Assessment</t>
+          <t>Complete Q4 Hospital Readiness Assessment</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>End of June</t>
+          <t>End of December</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5555,17 +5555,17 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>HRA submitted via REDCap. 2026 SPARK schedule is Q2 + Q4 (not the standard Q1 + Q4) — update templates before 2027 cohort.</t>
+          <t>HRA submitted via REDCap. 2026 SPARK schedule is Q2 + Q4 — see Notes on Q2 row.</t>
         </is>
       </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SPARK</t>
+          <t>TTT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5575,37 +5575,37 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Complete Q4 Hospital Readiness Assessment</t>
+          <t>Attend the January TTT initiative meeting</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>readiness_assessment</t>
+          <t>meeting_attendance</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>January</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>End of December</t>
+          <t>End of January</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5615,13 +5615,13 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>HRA submitted via REDCap. 2026 SPARK schedule is Q2 + Q4 — see Notes on Q2 row.</t>
+          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
         </is>
       </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Attend the January TTT initiative meeting</t>
+          <t>Attend the February TTT initiative meeting</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5660,12 +5660,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>February</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>End of January</t>
+          <t>End of February</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5681,7 +5681,7 @@
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Attend the February TTT initiative meeting</t>
+          <t>Attend the March TTT initiative meeting</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5720,12 +5720,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>March</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>End of February</t>
+          <t>End of March</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5741,7 +5741,7 @@
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -5755,17 +5755,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q2</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Attend the March TTT initiative meeting</t>
+          <t>Attend the April TTT initiative meeting</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>April</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>End of March</t>
+          <t>End of April</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5801,7 +5801,7 @@
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Attend the April TTT initiative meeting</t>
+          <t>Attend the May TTT initiative meeting</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>May</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>End of April</t>
+          <t>End of May</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5861,7 +5861,7 @@
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Attend the May TTT initiative meeting</t>
+          <t>Attend the June TTT initiative meeting</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>June</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>End of May</t>
+          <t>End of June</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5921,7 +5921,7 @@
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -5935,17 +5935,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Implementation Q3</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Attend the June TTT initiative meeting</t>
+          <t>Attend the July TTT initiative meeting</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>End of June</t>
+          <t>End of July</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5981,7 +5981,7 @@
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Attend the July TTT initiative meeting</t>
+          <t>Attend the August TTT initiative meeting</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>End of July</t>
+          <t>End of August</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -6041,7 +6041,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Attend the August TTT initiative meeting</t>
+          <t>Attend the September TTT initiative meeting</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>September</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>End of August</t>
+          <t>End of September</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6101,7 +6101,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -6115,17 +6115,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Attend the September TTT initiative meeting</t>
+          <t>Attend the October TTT initiative meeting</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6140,12 +6140,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>October</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>End of September</t>
+          <t>End of October</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6161,7 +6161,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Attend the October TTT initiative meeting</t>
+          <t>Attend the November TTT initiative meeting</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>November</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>End of October</t>
+          <t>End of November</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6221,7 +6221,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Attend the November TTT initiative meeting</t>
+          <t>Attend the December TTT initiative meeting</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>December</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>End of November</t>
+          <t>End of December</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6281,11 +6281,11 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TTT</t>
+          <t>SPARK</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6295,17 +6295,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Attend the December TTT initiative meeting</t>
+          <t>Attend the January SPARK initiative meeting</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>January</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>End of December</t>
+          <t>End of January</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6341,7 +6341,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Attend the January SPARK initiative meeting</t>
+          <t>Attend the February SPARK initiative meeting</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>February</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>End of January</t>
+          <t>End of February</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6401,7 +6401,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Attend the February SPARK initiative meeting</t>
+          <t>Attend the March SPARK initiative meeting</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>March</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>End of February</t>
+          <t>End of March</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6461,7 +6461,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -6475,17 +6475,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q2</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Attend the March SPARK initiative meeting</t>
+          <t>Attend the April SPARK initiative meeting</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6500,12 +6500,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>April</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>End of March</t>
+          <t>End of April</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6521,7 +6521,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Attend the April SPARK initiative meeting</t>
+          <t>Attend the May SPARK initiative meeting</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>May</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>End of April</t>
+          <t>End of May</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6581,7 +6581,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Attend the May SPARK initiative meeting</t>
+          <t>Attend the June SPARK initiative meeting</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>June</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>End of May</t>
+          <t>End of June</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6641,7 +6641,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -6655,17 +6655,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Implementation Q3</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Attend the June SPARK initiative meeting</t>
+          <t>Attend the July SPARK initiative meeting</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>End of June</t>
+          <t>End of July</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6701,7 +6701,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Attend the July SPARK initiative meeting</t>
+          <t>Attend the August SPARK initiative meeting</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>End of July</t>
+          <t>End of August</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6761,7 +6761,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Attend the August SPARK initiative meeting</t>
+          <t>Attend the September SPARK initiative meeting</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>September</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>End of August</t>
+          <t>End of September</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6821,7 +6821,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -6835,17 +6835,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Attend the September SPARK initiative meeting</t>
+          <t>Attend the October SPARK initiative meeting</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6860,12 +6860,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>October</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>End of September</t>
+          <t>End of October</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6881,7 +6881,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Attend the October SPARK initiative meeting</t>
+          <t>Attend the November SPARK initiative meeting</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>November</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>End of October</t>
+          <t>End of November</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6941,7 +6941,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Attend the November SPARK initiative meeting</t>
+          <t>Attend the December SPARK initiative meeting</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>December</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>End of November</t>
+          <t>End of December</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -7001,11 +7001,11 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SPARK</t>
+          <t>SOAR</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7015,17 +7015,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Attend the December SPARK initiative meeting</t>
+          <t>Attend the January SOAR initiative meeting</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>January</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>End of December</t>
+          <t>End of January</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -7061,7 +7061,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Attend the January SOAR initiative meeting</t>
+          <t>Attend the February SOAR initiative meeting</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>February</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>End of January</t>
+          <t>End of February</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -7121,7 +7121,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Attend the February SOAR initiative meeting</t>
+          <t>Attend the March SOAR initiative meeting</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>March</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>End of February</t>
+          <t>End of March</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7181,7 +7181,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -7195,17 +7195,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q2</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Attend the March SOAR initiative meeting</t>
+          <t>Attend the April SOAR initiative meeting</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -7220,12 +7220,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>April</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>End of March</t>
+          <t>End of April</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7241,7 +7241,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Attend the April SOAR initiative meeting</t>
+          <t>Attend the May SOAR initiative meeting</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -7280,12 +7280,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>May</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>End of April</t>
+          <t>End of May</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7301,7 +7301,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Attend the May SOAR initiative meeting</t>
+          <t>Attend the June SOAR initiative meeting</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -7340,12 +7340,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>June</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>End of May</t>
+          <t>End of June</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7361,7 +7361,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -7375,17 +7375,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Implementation Q3</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Attend the June SOAR initiative meeting</t>
+          <t>Attend the July SOAR initiative meeting</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>End of June</t>
+          <t>End of July</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7421,7 +7421,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Attend the July SOAR initiative meeting</t>
+          <t>Attend the August SOAR initiative meeting</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>End of July</t>
+          <t>End of August</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7481,7 +7481,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Attend the August SOAR initiative meeting</t>
+          <t>Attend the September SOAR initiative meeting</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7520,12 +7520,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>September</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>End of August</t>
+          <t>End of September</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7541,7 +7541,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -7555,17 +7555,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Attend the September SOAR initiative meeting</t>
+          <t>Attend the October SOAR initiative meeting</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>October</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>End of September</t>
+          <t>End of October</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7601,7 +7601,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Attend the October SOAR initiative meeting</t>
+          <t>Attend the November SOAR initiative meeting</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>November</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>End of October</t>
+          <t>End of November</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7661,7 +7661,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Attend the November SOAR initiative meeting</t>
+          <t>Attend the December SOAR initiative meeting</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -7700,12 +7700,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>December</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>End of November</t>
+          <t>End of December</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7721,11 +7721,11 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SOAR</t>
+          <t>NEST</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7735,17 +7735,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Implementation Q4</t>
+          <t>Implementation Q1</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Attend the December SOAR initiative meeting</t>
+          <t>Attend the January NEST initiative meeting</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -7760,12 +7760,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>January</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>End of December</t>
+          <t>End of January</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7781,7 +7781,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Attend the January NEST initiative meeting</t>
+          <t>Attend the February NEST initiative meeting</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>February</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>End of January</t>
+          <t>End of February</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7841,7 +7841,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Attend the February NEST initiative meeting</t>
+          <t>Attend the March NEST initiative meeting</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>March</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>End of February</t>
+          <t>End of March</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7901,7 +7901,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -7915,17 +7915,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Implementation Q1</t>
+          <t>Implementation Q2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Attend the March NEST initiative meeting</t>
+          <t>Attend the April NEST initiative meeting</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7940,12 +7940,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>April</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>End of March</t>
+          <t>End of April</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7961,7 +7961,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Attend the April NEST initiative meeting</t>
+          <t>Attend the May NEST initiative meeting</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8000,12 +8000,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>May</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>End of April</t>
+          <t>End of May</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -8021,7 +8021,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Attend the May NEST initiative meeting</t>
+          <t>Attend the June NEST initiative meeting</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>June</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>End of May</t>
+          <t>End of June</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -8081,7 +8081,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -8095,17 +8095,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Implementation Q2</t>
+          <t>Implementation Q3</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Attend the June NEST initiative meeting</t>
+          <t>Attend the July NEST initiative meeting</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>July</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>End of June</t>
+          <t>End of July</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -8141,7 +8141,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Attend the July NEST initiative meeting</t>
+          <t>Attend the August NEST initiative meeting</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>August</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>End of July</t>
+          <t>End of August</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8201,7 +8201,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Attend the August NEST initiative meeting</t>
+          <t>Attend the September NEST initiative meeting</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>September</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>End of August</t>
+          <t>End of September</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8261,7 +8261,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -8275,17 +8275,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Implementation Q3</t>
+          <t>Implementation Q4</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Attend the September NEST initiative meeting</t>
+          <t>Attend the October NEST initiative meeting</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>October</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>End of September</t>
+          <t>End of October</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8321,7 +8321,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Attend the October NEST initiative meeting</t>
+          <t>Attend the November NEST initiative meeting</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -8360,12 +8360,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>November</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>End of October</t>
+          <t>End of November</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8381,7 +8381,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Attend the November NEST initiative meeting</t>
+          <t>Attend the December NEST initiative meeting</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>December</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>End of November</t>
+          <t>End of December</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8434,66 +8434,6 @@
         </is>
       </c>
       <c r="M127" t="inlineStr">
-        <is>
-          <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>143</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>NEST</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Implementation Q4</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Attend the December NEST initiative meeting</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>meeting_attendance</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>December</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>End of December</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
         <is>
           <t>Annual requirement: at least 9 of 12 monthly meetings. Annual Forum attendance counts toward the month it falls in (September in 2026).</t>
         </is>
